--- a/xy10102/output/feature_importance.xlsx
+++ b/xy10102/output/feature_importance.xlsx
@@ -52,24 +52,24 @@
     <t>rolling_std_6h</t>
   </si>
   <si>
+    <t>charging_duration</t>
+  </si>
+  <si>
     <t>rolling_mean_12h</t>
   </si>
   <si>
-    <t>charging_duration</t>
-  </si>
-  <si>
     <t>rolling_std_3h</t>
   </si>
   <si>
     <t>rolling_std_12h</t>
   </si>
   <si>
+    <t>lag_168h</t>
+  </si>
+  <si>
     <t>rolling_mean_6h</t>
   </si>
   <si>
-    <t>lag_168h</t>
-  </si>
-  <si>
     <t>lag_24h</t>
   </si>
   <si>
@@ -91,31 +91,31 @@
     <t>day_of_week</t>
   </si>
   <si>
+    <t>day_cos</t>
+  </si>
+  <si>
     <t>hour_cos</t>
   </si>
   <si>
-    <t>day_cos</t>
-  </si>
-  <si>
     <t>is_weekend</t>
   </si>
   <si>
+    <t>month</t>
+  </si>
+  <si>
     <t>price_medium</t>
   </si>
   <si>
-    <t>month</t>
-  </si>
-  <si>
     <t>price_above_mean</t>
   </si>
   <si>
     <t>price_high</t>
   </si>
   <si>
+    <t>price_low</t>
+  </si>
+  <si>
     <t>price_very_high</t>
-  </si>
-  <si>
-    <t>price_low</t>
   </si>
   <si>
     <t>is_holiday</t>
@@ -492,7 +492,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.7675663535612174</v>
+        <v>0.7676385149911348</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -500,7 +500,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.06439023352627442</v>
+        <v>0.06681909193316861</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -508,7 +508,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.0410173161105694</v>
+        <v>0.03836262255895533</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -516,7 +516,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.03198679337098435</v>
+        <v>0.03444168978167005</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -524,7 +524,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.02778970650603548</v>
+        <v>0.02617275244077258</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -532,7 +532,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0.02359356026056364</v>
+        <v>0.02171818324508148</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -540,7 +540,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.01219459027962689</v>
+        <v>0.01256987830915612</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -548,7 +548,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.006063287881194622</v>
+        <v>0.006363979316537505</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -556,7 +556,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>0.00471586904578396</v>
+        <v>0.004880069435841612</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -564,7 +564,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>0.003147239512424558</v>
+        <v>0.003285915664628655</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -572,7 +572,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>0.002597201986667203</v>
+        <v>0.002785035288907902</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -580,7 +580,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>0.002101706355367426</v>
+        <v>0.002427804095218095</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -588,7 +588,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>0.002059232295731881</v>
+        <v>0.002375414214487647</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -596,7 +596,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>0.002045880796835265</v>
+        <v>0.002251521660344221</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -604,7 +604,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>0.001939858106764778</v>
+        <v>0.001497342943629004</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -612,7 +612,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.001377961307209654</v>
+        <v>0.001399896404077875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -620,7 +620,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.001369829080138354</v>
+        <v>0.001298341426601112</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -628,7 +628,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>0.001052310950399048</v>
+        <v>0.0007598670269595895</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -636,7 +636,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>0.0007721450166408179</v>
+        <v>0.0007252244627290036</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -644,7 +644,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>0.0005130178733257259</v>
+        <v>0.0005471428815667591</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -652,7 +652,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>0.000405050476168748</v>
+        <v>0.0004245420440860171</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -660,7 +660,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>0.0003900658837589383</v>
+        <v>0.000302976855506272</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -668,7 +668,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>0.0002719544557950868</v>
+        <v>0.0002468864981334053</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -676,7 +676,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>0.0002277119827101424</v>
+        <v>0.0002086942648481832</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -684,7 +684,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>0.0002038109036986308</v>
+        <v>0.0001839082351540209</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -692,7 +692,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>6.055509005965359E-05</v>
+        <v>0.0001346816697149236</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -700,7 +700,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>6.00257213346175E-05</v>
+        <v>8.208867270027505E-05</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -708,7 +708,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>5.906969970475835E-05</v>
+        <v>5.477093502050877E-05</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -716,7 +716,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>1.99761170077924E-05</v>
+        <v>2.407909200681588E-05</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -724,7 +724,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>4.834978788689001E-06</v>
+        <v>1.418671875485931E-05</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -732,7 +732,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>2.083950483838125E-06</v>
+        <v>1.766798302148073E-06</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -740,7 +740,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>7.669167344119409E-07</v>
+        <v>1.130134304586103E-06</v>
       </c>
     </row>
     <row r="34" spans="1:2">
